--- a/event_registration_forms/022_pet_first_aid_training_registration--event_registration_forms.xlsx
+++ b/event_registration_forms/022_pet_first_aid_training_registration--event_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -951,12 +951,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'morning'}</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Morning'}</t>
+          <t>Morning</t>
         </is>
       </c>
     </row>
@@ -968,12 +968,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'afternoon'}</t>
+          <t>afternoon</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Afternoon'}</t>
+          <t>Afternoon</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'evening'}</t>
+          <t>evening</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Evening'}</t>
+          <t>Evening</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'dog'}</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Dog'}</t>
+          <t>Dog</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'cat'}</t>
+          <t>cat</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Cat'}</t>
+          <t>Cat</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'basic'}</t>
+          <t>basic</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Basic'}</t>
+          <t>Basic</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'advanced'}</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Advanced'}</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
@@ -1087,12 +1087,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'refresher'}</t>
+          <t>refresher</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Refresher'}</t>
+          <t>Refresher</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'bank_transfer_(eft)'}</t>
+          <t>bank_transfer_(eft)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Bank Transfer (EFT)'}</t>
+          <t>Bank Transfer (EFT)</t>
         </is>
       </c>
     </row>
@@ -1121,12 +1121,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'cash'}</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Cash'}</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
@@ -1138,12 +1138,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'i_understand_that_by_signing_this_form,_i_am_confirming_that_i_have_read_the_course_policies.'}</t>
+          <t>i_understand_that_by_signing_this_form,_i_am_confirming_that_i_have_read_the_course_policies.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'I understand that by signing this form, I am confirming that I have read the course policies.'}</t>
+          <t>I understand that by signing this form, I am confirming that I have read the course policies.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1172,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'paid'}</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Paid'}</t>
+          <t>Paid</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
